--- a/math/04数和式.xlsx
+++ b/math/04数和式.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABDDECF-2ABB-F14D-9EDA-A27391744355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AA05BE-BC8B-2A45-A26C-2AD7CC4AD943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{BA96F506-D2D0-3E4E-9EA2-ABC6D0F7306A}"/>
   </bookViews>
@@ -53,10 +53,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>有理数：由整数（正整数、0、负整数）和分数（正负数、负分数）组成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>减法 转化为加相反数，即a-b=a+(-b)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,6 +195,10 @@
   </si>
   <si>
     <t>单项式乘单项式（系数、同字母幂相乘，指数相加）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有理数：由整数（正整数、0、负整数）和分数（正分数、负分数）组成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -620,72 +620,72 @@
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.15">
       <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.15">
       <c r="D10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.15">
@@ -696,95 +696,95 @@
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C25" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.15">
       <c r="D26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C28" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="J30" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.15">
       <c r="D31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.15">
       <c r="J32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="3:10" x14ac:dyDescent="0.15">
       <c r="C33" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="3:10" x14ac:dyDescent="0.15">
       <c r="D34" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="3:10" x14ac:dyDescent="0.15">
       <c r="D35" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.15">
       <c r="C37" s="2"/>
       <c r="D37" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="3:10" x14ac:dyDescent="0.15">
       <c r="C38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="39" spans="3:10" x14ac:dyDescent="0.15">
       <c r="D39" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="3:10" x14ac:dyDescent="0.15">

--- a/math/04数和式.xlsx
+++ b/math/04数和式.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/math/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AA05BE-BC8B-2A45-A26C-2AD7CC4AD943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEC1D28-AD22-3541-92B9-85403AB0044F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{BA96F506-D2D0-3E4E-9EA2-ABC6D0F7306A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>2、</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -199,6 +199,30 @@
   </si>
   <si>
     <t>有理数：由整数（正整数、0、负整数）和分数（正分数、负分数）组成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>形如 A/B（A和B为整式，B含字母且B不等于0）分母为0无意义，分子为0且分母非0时值为0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>除法：转化为乘倒数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加减法：同分母分母不变分子相加减，异分母先通分后加减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乘法：分子乘分子，分母乘分母，能约分的先约分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -744,7 +768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="3:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C33" s="1" t="s">
         <v>26</v>
       </c>
@@ -755,7 +779,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="3:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.15">
       <c r="D34" s="1" t="s">
         <v>24</v>
       </c>
@@ -763,18 +787,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="3:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.15">
       <c r="D35" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="3:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C37" s="2"/>
       <c r="D37" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="38" spans="3:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.15">
       <c r="C38" s="1" t="s">
         <v>30</v>
       </c>
@@ -782,13 +806,38 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="3:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.15">
       <c r="D39" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="3:10" x14ac:dyDescent="0.15">
-      <c r="C42" s="2"/>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="C44" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="C46" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="C47" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="C48" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C65" s="2"/>
